--- a/artfynd/A 54110-2024 artfynd.xlsx
+++ b/artfynd/A 54110-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,46 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54239583</v>
+        <v>54239589</v>
       </c>
       <c r="B2" t="n">
-        <v>96368</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108194</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223619</v>
+        <v>220103</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ängsnattviol</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. bifolia</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+          <t>Crepis praemorsa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Falkhammar SSV 550 m, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>680523.1703803877</v>
+        <v>680523</v>
       </c>
       <c r="R2" t="n">
-        <v>6628369.964131673</v>
+        <v>6628370</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -744,19 +752,9 @@
           <t>2015-07-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-07-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,59 +786,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>54239589</v>
+        <v>54239595</v>
       </c>
       <c r="B3" t="n">
-        <v>105123</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220103</v>
+        <v>221141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Falkhammar SSV 550 m, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680523.1703803877</v>
+        <v>680523</v>
       </c>
       <c r="R3" t="n">
-        <v>6628369.964131673</v>
+        <v>6628370</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,19 +854,9 @@
           <t>2015-07-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-07-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,32 +888,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>54239595</v>
+        <v>54239591</v>
       </c>
       <c r="B4" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221141</v>
+        <v>222133</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -954,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680523.1703803877</v>
+        <v>680523</v>
       </c>
       <c r="R4" t="n">
-        <v>6628369.964131673</v>
+        <v>6628370</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,19 +956,9 @@
           <t>2015-07-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-07-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,6 +987,104 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>54239583</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99154</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223619</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ängsnattviol</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. bifolia</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Falkhammar SSV 550 m, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>680523</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6628370</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fasterna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2015-07-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2015-07-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Ohävdad ängsbacke vid liten vall.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54110-2024 artfynd.xlsx
+++ b/artfynd/A 54110-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54239589</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54239595</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54239591</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,8 +1105,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54239583</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>